--- a/main_data/contrafactual_num_vinculaciones_wompi.xlsx
+++ b/main_data/contrafactual_num_vinculaciones_wompi.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,6 +714,23 @@
         <v>0.514114076009611</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B17" t="n">
+        <v>27466.729033014</v>
+      </c>
+      <c r="C17" t="n">
+        <v>70977</v>
+      </c>
+      <c r="D17" t="n">
+        <v>43510.27096698601</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6130193015622808</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
